--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3293-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3293-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6962EBE-B9BC-4BEF-BA7B-EFFD178CE71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3A4C20B-4938-4376-A7FE-EE27E4C33826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{820E7F62-E29B-413C-9CE0-A37BE997034D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3A1DBE78-093C-45CA-BD64-99D401C9C180}"/>
   </bookViews>
   <sheets>
     <sheet name="3293-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,21 +1451,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F62F41-2A3A-474C-87A8-C7EB27CB1AB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C416CA-2E9A-45EE-861C-C93C885C2F7B}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1493,7 +1493,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1619,7 +1619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <v>2023</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2021</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2020</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2019</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2018</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2017</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2016</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2015</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2014</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2013</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2012</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2011</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2010</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2009</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2008</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2007</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2006</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2005</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2004</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40" t="s">
         <v>35</v>
       </c>
